--- a/stories/arbres/TREE-COL-035.xlsx
+++ b/stories/arbres/TREE-COL-035.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Corentin tient la main de maman au marché. Maman dit : on salue. On dit bonjour. On dit s'il te plaît. On dit merci. Corentin répète les trois mots.</t>
+          <t>Corentin tient la main de maman au marché. On salue. On dit bonjour. On dit s'il te plaît. On dit merci. Corentin répète les trois mots.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Corentin tient la main de maman au marché.
+maman|On salue. On dit bonjour. On dit s'il te plaît. On dit merci.
+narrateur|Corentin répète les trois mots.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1511,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la boulangerie, l'étal, ou la fromagerie.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1649,6 +1678,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|À la boulangerie, Corentin dit bonjour. S'il te plaît. Merci.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1859,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|À la boulangerie, quels mots ?</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2032,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Corentin a dit bonjour, s'il te plaît, merci.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2223,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la boulangère, le voisin, ou la maîtresse.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2341,6 +2390,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Corentin dit bonjour. S'il te plaît. Merci.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2527,6 +2581,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le pain, une pomme, ou un fromage.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2689,6 +2748,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Corentin rejoint la boulangère à la boulangerie. Il a le pain. Bonjour, s'il te plaît, merci.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2851,6 +2915,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3013,6 +3082,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Corentin rejoint la boulangère à la boulangerie. Il a une pomme. Bonjour, s'il te plaît, merci.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3175,6 +3249,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3337,6 +3416,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Corentin rejoint la boulangère à la boulangerie. Il a un fromage. Bonjour, s'il te plaît, merci.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3499,6 +3583,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3661,6 +3750,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Corentin dit bonjour. S'il te plaît. Merci.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3847,6 +3941,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le pain, une pomme, ou un fromage.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4009,6 +4108,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Corentin rejoint le voisin à la boulangerie. Il a le pain. Bonjour, s'il te plaît, merci.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4171,6 +4275,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4333,6 +4442,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Corentin rejoint le voisin à la boulangerie. Il a une pomme. Bonjour, s'il te plaît, merci.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4495,6 +4609,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4657,6 +4776,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Corentin rejoint le voisin à la boulangerie. Il a un fromage. Bonjour, s'il te plaît, merci.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4819,6 +4943,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4981,6 +5110,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Corentin dit bonjour. S'il te plaît. Merci.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5167,6 +5301,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le pain, une pomme, ou un fromage.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5329,6 +5468,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Corentin rejoint la maîtresse à la boulangerie. Il a le pain. Bonjour, s'il te plaît, merci.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5491,6 +5635,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5653,6 +5802,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Corentin rejoint la maîtresse à la boulangerie. Il a une pomme. Bonjour, s'il te plaît, merci.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5815,6 +5969,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5977,6 +6136,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Corentin rejoint la maîtresse à la boulangerie. Il a un fromage. Bonjour, s'il te plaît, merci.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6139,6 +6303,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6301,6 +6470,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|À l'étal, Corentin dit bonjour. S'il te plaît. Merci.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6477,6 +6651,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|À l'étal, quels mots ?</t>
         </is>
       </c>
     </row>
@@ -6641,6 +6820,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Les trois mots.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6827,6 +7011,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la boulangère, le voisin, ou la maîtresse.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6989,6 +7178,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Corentin dit bonjour. S'il te plaît. Merci.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7175,6 +7369,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le pain, une pomme, ou un fromage.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7337,6 +7536,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Corentin rejoint la boulangère à l'étal. Il a le pain. Bonjour, s'il te plaît, merci.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7499,6 +7703,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7661,6 +7870,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Corentin rejoint la boulangère à l'étal. Il a une pomme. Bonjour, s'il te plaît, merci.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7823,6 +8037,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7985,6 +8204,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Corentin rejoint la boulangère à l'étal. Il a un fromage. Bonjour, s'il te plaît, merci.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8147,6 +8371,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8309,6 +8538,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Corentin dit bonjour. S'il te plaît. Merci.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8495,6 +8729,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le pain, une pomme, ou un fromage.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8657,6 +8896,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Corentin rejoint le voisin à l'étal. Il a le pain. Bonjour, s'il te plaît, merci.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8819,6 +9063,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8981,6 +9230,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Corentin rejoint le voisin à l'étal. Il a une pomme. Bonjour, s'il te plaît, merci.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9143,6 +9397,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9305,6 +9564,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Corentin rejoint le voisin à l'étal. Il a un fromage. Bonjour, s'il te plaît, merci.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9467,6 +9731,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9629,6 +9898,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Corentin dit bonjour. S'il te plaît. Merci.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9815,6 +10089,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le pain, une pomme, ou un fromage.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9977,6 +10256,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Corentin rejoint la maîtresse à l'étal. Il a le pain. Bonjour, s'il te plaît, merci.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10139,6 +10423,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10301,6 +10590,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Corentin rejoint la maîtresse à l'étal. Il a une pomme. Bonjour, s'il te plaît, merci.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10463,6 +10757,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10625,6 +10924,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Corentin rejoint la maîtresse à l'étal. Il a un fromage. Bonjour, s'il te plaît, merci.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10787,6 +11091,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10949,6 +11258,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|À la fromagerie, Corentin dit bonjour. S'il te plaît. Merci.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11125,6 +11439,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|À la fromagerie, quels mots ?</t>
         </is>
       </c>
     </row>
@@ -11289,6 +11608,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Corentin a salué.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11475,6 +11799,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la boulangère, le voisin, ou la maîtresse.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11637,6 +11966,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Corentin dit bonjour. S'il te plaît. Merci.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11823,6 +12157,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le pain, une pomme, ou un fromage.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -11985,6 +12324,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Corentin rejoint la boulangère à la fromagerie. Il a le pain. Bonjour, s'il te plaît, merci.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12147,6 +12491,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12309,6 +12658,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Corentin rejoint la boulangère à la fromagerie. Il a une pomme. Bonjour, s'il te plaît, merci.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12471,6 +12825,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12633,6 +12992,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Corentin rejoint la boulangère à la fromagerie. Il a un fromage. Bonjour, s'il te plaît, merci.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12795,6 +13159,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12957,6 +13326,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Corentin dit bonjour. S'il te plaît. Merci.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13143,6 +13517,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le pain, une pomme, ou un fromage.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13305,6 +13684,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Corentin rejoint le voisin à la fromagerie. Il a le pain. Bonjour, s'il te plaît, merci.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13467,6 +13851,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13629,6 +14018,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Corentin rejoint le voisin à la fromagerie. Il a une pomme. Bonjour, s'il te plaît, merci.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13791,6 +14185,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13953,6 +14352,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Corentin rejoint le voisin à la fromagerie. Il a un fromage. Bonjour, s'il te plaît, merci.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14115,6 +14519,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14277,6 +14686,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Corentin dit bonjour. S'il te plaît. Merci.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14463,6 +14877,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le pain, une pomme, ou un fromage.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14625,6 +15044,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Corentin rejoint la maîtresse à la fromagerie. Il a le pain. Bonjour, s'il te plaît, merci.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14787,6 +15211,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14949,6 +15378,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Corentin rejoint la maîtresse à la fromagerie. Il a une pomme. Bonjour, s'il te plaît, merci.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15111,6 +15545,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15273,6 +15712,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Corentin rejoint la maîtresse à la fromagerie. Il a un fromage. Bonjour, s'il te plaît, merci.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15435,6 +15879,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15453,7 +15902,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15470,6 +15919,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-COL-035.xlsx
+++ b/stories/arbres/TREE-COL-035.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1325,6 +1330,7 @@
 narrateur|Corentin répète les trois mots.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1516,6 +1522,7 @@
           <t>narrateur|On peut prendre la boulangerie, l'étal, ou la fromagerie.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1683,6 +1690,7 @@
           <t>narrateur|À la boulangerie, Corentin dit bonjour. S'il te plaît. Merci.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1866,6 +1874,7 @@
           <t>narrateur|À la boulangerie, quels mots ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2037,6 +2046,7 @@
           <t>narrateur|Corentin a dit bonjour, s'il te plaît, merci.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2228,6 +2238,7 @@
           <t>narrateur|On peut prendre la boulangère, le voisin, ou la maîtresse.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2395,6 +2406,7 @@
           <t>narrateur|Corentin dit bonjour. S'il te plaît. Merci.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2586,6 +2598,7 @@
           <t>narrateur|On peut prendre le pain, une pomme, ou un fromage.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2753,6 +2766,7 @@
           <t>narrateur|Corentin rejoint la boulangère à la boulangerie. Il a le pain. Bonjour, s'il te plaît, merci.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2920,6 +2934,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3087,6 +3102,7 @@
           <t>narrateur|Corentin rejoint la boulangère à la boulangerie. Il a une pomme. Bonjour, s'il te plaît, merci.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3254,6 +3270,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3421,6 +3438,7 @@
           <t>narrateur|Corentin rejoint la boulangère à la boulangerie. Il a un fromage. Bonjour, s'il te plaît, merci.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3588,6 +3606,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3755,6 +3774,7 @@
           <t>narrateur|Corentin dit bonjour. S'il te plaît. Merci.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3946,6 +3966,7 @@
           <t>narrateur|On peut prendre le pain, une pomme, ou un fromage.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4113,6 +4134,7 @@
           <t>narrateur|Corentin rejoint le voisin à la boulangerie. Il a le pain. Bonjour, s'il te plaît, merci.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4280,6 +4302,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4447,6 +4470,7 @@
           <t>narrateur|Corentin rejoint le voisin à la boulangerie. Il a une pomme. Bonjour, s'il te plaît, merci.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4614,6 +4638,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4781,6 +4806,7 @@
           <t>narrateur|Corentin rejoint le voisin à la boulangerie. Il a un fromage. Bonjour, s'il te plaît, merci.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4948,6 +4974,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5115,6 +5142,7 @@
           <t>narrateur|Corentin dit bonjour. S'il te plaît. Merci.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5306,6 +5334,7 @@
           <t>narrateur|On peut prendre le pain, une pomme, ou un fromage.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5473,6 +5502,7 @@
           <t>narrateur|Corentin rejoint la maîtresse à la boulangerie. Il a le pain. Bonjour, s'il te plaît, merci.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5640,6 +5670,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5807,6 +5838,7 @@
           <t>narrateur|Corentin rejoint la maîtresse à la boulangerie. Il a une pomme. Bonjour, s'il te plaît, merci.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5974,6 +6006,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6141,6 +6174,7 @@
           <t>narrateur|Corentin rejoint la maîtresse à la boulangerie. Il a un fromage. Bonjour, s'il te plaît, merci.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6308,6 +6342,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6475,6 +6510,7 @@
           <t>narrateur|À l'étal, Corentin dit bonjour. S'il te plaît. Merci.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6658,6 +6694,7 @@
           <t>narrateur|À l'étal, quels mots ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6825,6 +6862,7 @@
           <t>narrateur|Oui. Les trois mots.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7016,6 +7054,7 @@
           <t>narrateur|On peut prendre la boulangère, le voisin, ou la maîtresse.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7183,6 +7222,7 @@
           <t>narrateur|Corentin dit bonjour. S'il te plaît. Merci.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7374,6 +7414,7 @@
           <t>narrateur|On peut prendre le pain, une pomme, ou un fromage.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7541,6 +7582,7 @@
           <t>narrateur|Corentin rejoint la boulangère à l'étal. Il a le pain. Bonjour, s'il te plaît, merci.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7708,6 +7750,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7875,6 +7918,7 @@
           <t>narrateur|Corentin rejoint la boulangère à l'étal. Il a une pomme. Bonjour, s'il te plaît, merci.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8042,6 +8086,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8209,6 +8254,7 @@
           <t>narrateur|Corentin rejoint la boulangère à l'étal. Il a un fromage. Bonjour, s'il te plaît, merci.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8376,6 +8422,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8543,6 +8590,7 @@
           <t>narrateur|Corentin dit bonjour. S'il te plaît. Merci.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8734,6 +8782,7 @@
           <t>narrateur|On peut prendre le pain, une pomme, ou un fromage.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8901,6 +8950,7 @@
           <t>narrateur|Corentin rejoint le voisin à l'étal. Il a le pain. Bonjour, s'il te plaît, merci.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9068,6 +9118,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9235,6 +9286,7 @@
           <t>narrateur|Corentin rejoint le voisin à l'étal. Il a une pomme. Bonjour, s'il te plaît, merci.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9402,6 +9454,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9569,6 +9622,7 @@
           <t>narrateur|Corentin rejoint le voisin à l'étal. Il a un fromage. Bonjour, s'il te plaît, merci.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9736,6 +9790,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9903,6 +9958,7 @@
           <t>narrateur|Corentin dit bonjour. S'il te plaît. Merci.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10094,6 +10150,7 @@
           <t>narrateur|On peut prendre le pain, une pomme, ou un fromage.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10261,6 +10318,7 @@
           <t>narrateur|Corentin rejoint la maîtresse à l'étal. Il a le pain. Bonjour, s'il te plaît, merci.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10428,6 +10486,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10595,6 +10654,7 @@
           <t>narrateur|Corentin rejoint la maîtresse à l'étal. Il a une pomme. Bonjour, s'il te plaît, merci.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10762,6 +10822,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10929,6 +10990,7 @@
           <t>narrateur|Corentin rejoint la maîtresse à l'étal. Il a un fromage. Bonjour, s'il te plaît, merci.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11096,6 +11158,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11263,6 +11326,7 @@
           <t>narrateur|À la fromagerie, Corentin dit bonjour. S'il te plaît. Merci.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11446,6 +11510,7 @@
           <t>narrateur|À la fromagerie, quels mots ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11613,6 +11678,7 @@
           <t>narrateur|Corentin a salué.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11804,6 +11870,7 @@
           <t>narrateur|On peut prendre la boulangère, le voisin, ou la maîtresse.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11971,6 +12038,7 @@
           <t>narrateur|Corentin dit bonjour. S'il te plaît. Merci.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12162,6 +12230,7 @@
           <t>narrateur|On peut prendre le pain, une pomme, ou un fromage.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12329,6 +12398,7 @@
           <t>narrateur|Corentin rejoint la boulangère à la fromagerie. Il a le pain. Bonjour, s'il te plaît, merci.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12496,6 +12566,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12663,6 +12734,7 @@
           <t>narrateur|Corentin rejoint la boulangère à la fromagerie. Il a une pomme. Bonjour, s'il te plaît, merci.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12830,6 +12902,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12997,6 +13070,7 @@
           <t>narrateur|Corentin rejoint la boulangère à la fromagerie. Il a un fromage. Bonjour, s'il te plaît, merci.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13164,6 +13238,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13331,6 +13406,7 @@
           <t>narrateur|Corentin dit bonjour. S'il te plaît. Merci.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13522,6 +13598,7 @@
           <t>narrateur|On peut prendre le pain, une pomme, ou un fromage.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13689,6 +13766,7 @@
           <t>narrateur|Corentin rejoint le voisin à la fromagerie. Il a le pain. Bonjour, s'il te plaît, merci.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13856,6 +13934,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14023,6 +14102,7 @@
           <t>narrateur|Corentin rejoint le voisin à la fromagerie. Il a une pomme. Bonjour, s'il te plaît, merci.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14190,6 +14270,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14357,6 +14438,7 @@
           <t>narrateur|Corentin rejoint le voisin à la fromagerie. Il a un fromage. Bonjour, s'il te plaît, merci.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14524,6 +14606,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14691,6 +14774,7 @@
           <t>narrateur|Corentin dit bonjour. S'il te plaît. Merci.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14882,6 +14966,7 @@
           <t>narrateur|On peut prendre le pain, une pomme, ou un fromage.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15049,6 +15134,7 @@
           <t>narrateur|Corentin rejoint la maîtresse à la fromagerie. Il a le pain. Bonjour, s'il te plaît, merci.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15216,6 +15302,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15383,6 +15470,7 @@
           <t>narrateur|Corentin rejoint la maîtresse à la fromagerie. Il a une pomme. Bonjour, s'il te plaît, merci.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15550,6 +15638,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15717,6 +15806,7 @@
           <t>narrateur|Corentin rejoint la maîtresse à la fromagerie. Il a un fromage. Bonjour, s'il te plaît, merci.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15884,6 +15974,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15902,7 +15993,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15926,6 +16017,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15940,7 +16045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16127,6 +16232,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-COL-035.xlsx
+++ b/stories/arbres/TREE-COL-035.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Corentin dit bonjour, s'il te plaît, merci</t>
+          <t>Le store goutteux et les trois mots</t>
         </is>
       </c>
     </row>
@@ -843,6 +843,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sous le store goutteux du marché, Raphaël tient le panier troué. Il dit bonjour, s'il te plaît, merci, à chaque étal, avec papa et maman.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Corentin tient la main de maman au marché. On salue. On dit bonjour. On dit s'il te plaît. On dit merci. Corentin répète les trois mots.</t>
+          <t>Un store rayé goutte encore, au-dessus des caisses. Une goutte tombe sur le pavé. Elle fait un petit cercle, tout brillant. Un pigeon picore une miette, près d'une caisse. La caisse sent le bois mouillé. Ça sent le pain chaud, déjà. Papa porte un panier d'osier. Le panier a un trou, tout petit. Maman noue l'écharpe de Raphaël. L'écharpe est rouge, un peu rêche. Tu as vu le pigeon ? Il a une miette. Le store est encore mouillé. En ce moment, Raphaël touche le panier. L'osier pique un peu, puis cède. On marche vers les étals. On dit les mots, au marché. On dit bonjour. On dit s'il te plaît. On dit merci. Bonjour. Bravo, Raphaël. Une autre goutte tombe, sur la chaussure. La chaussure fait un petit toc, sur le pavé.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,12 +1337,37 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Corentin tient la main de maman au marché.
-maman|On salue. On dit bonjour. On dit s'il te plaît. On dit merci.
-narrateur|Corentin répète les trois mots.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Un store rayé goutte encore, au-dessus des caisses.
+narrateur|Une goutte tombe sur le pavé.
+narrateur|Elle fait un petit cercle, tout brillant.
+narrateur|Un pigeon picore une miette, près d'une caisse.
+narrateur|La caisse sent le bois mouillé.
+narrateur|Ça sent le pain chaud, déjà.
+narrateur|Papa porte un panier d'osier.
+narrateur|Le panier a un trou, tout petit.
+narrateur|Maman noue l'écharpe de Raphaël.
+narrateur|L'écharpe est rouge, un peu rêche.
+papa|Tu as vu le pigeon ?
+enfant-m|Il a une miette.
+maman|Le store est encore mouillé.
+narrateur|En ce moment, Raphaël touche le panier.
+narrateur|L'osier pique un peu, puis cède.
+papa|On marche vers les étals.
+maman|On dit les mots, au marché.
+maman|On dit bonjour.
+maman|On dit s'il te plaît.
+maman|On dit merci.
+enfant-m|Bonjour.
+papa|Bravo, Raphaël.
+narrateur|Une autre goutte tombe, sur la chaussure.
+narrateur|La chaussure fait un petit toc, sur le pavé.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>goutte,oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1355,7 +1392,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre la boulangerie, l'étal, ou la fromagerie.</t>
+          <t>Trois coins du marché attendent. La boulangerie, l'étal, ou la fromagerie ? On dit bonjour. On dit merci.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1519,7 +1556,10 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre la boulangerie, l'étal, ou la fromagerie.</t>
+          <t>narrateur|Trois coins du marché attendent.
+papa|La boulangerie, l'étal, ou la fromagerie ?
+maman|On dit bonjour.
+maman|On dit merci.</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1547,7 +1587,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>À la boulangerie, Corentin dit bonjour. S'il te plaît. Merci.</t>
+          <t>Raphaël pousse la porte de la boulangerie. Une petite cloche fait ding. L'air chaud sent le beurre. De la farine blanche reste sur le bois. Les croûtes dorées sont alignées. Papa pose le panier, tout près. Bonjour. Bonjour. On dit bonjour. On dit s'il te plaît. On dit merci. Un petit pain attend derrière la vitre. Tu veux celui-là ? Oui. S'il te plaît. Le sachet papier fait un bruit doux. Merci. Bravo, Raphaël. Tu as dit les trois mots. Le pain reste tiède contre le manteau.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1687,10 +1727,33 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|À la boulangerie, Corentin dit bonjour. S'il te plaît. Merci.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Raphaël pousse la porte de la boulangerie.
+narrateur|Une petite cloche fait ding.
+narrateur|L'air chaud sent le beurre.
+narrateur|De la farine blanche reste sur le bois.
+narrateur|Les croûtes dorées sont alignées.
+narrateur|Papa pose le panier, tout près.
+enfant-m|Bonjour.
+papa|Bonjour.
+maman|On dit bonjour.
+maman|On dit s'il te plaît.
+maman|On dit merci.
+narrateur|Un petit pain attend derrière la vitre.
+papa|Tu veux celui-là ?
+enfant-m|Oui.
+enfant-m|S'il te plaît.
+narrateur|Le sachet papier fait un bruit doux.
+enfant-m|Merci.
+maman|Bravo, Raphaël.
+maman|Tu as dit les trois mots.
+narrateur|Le pain reste tiède contre le manteau.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>cloche</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1715,7 +1778,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>À la boulangerie, quels mots ?</t>
+          <t>Raphaël veut le petit pain. Il dit quoi ?</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1871,7 +1934,8 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|À la boulangerie, quels mots ?</t>
+          <t>narrateur|Raphaël veut le petit pain.
+maman|Il dit quoi ?</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1899,7 +1963,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Corentin a dit bonjour, s'il te plaît, merci.</t>
+          <t>Oui. On dit bonjour. On dit s'il te plaît. On dit merci. Raphaël souffle un peu. Le sachet reste tiède dans ses mains. Bonjour. Merci. Bravo, Raphaël. C'est du bon travail. La cloche reste silencieuse, un moment.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2043,7 +2107,17 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Corentin a dit bonjour, s'il te plaît, merci.</t>
+          <t>maman|Oui.
+maman|On dit bonjour.
+maman|On dit s'il te plaît.
+maman|On dit merci.
+narrateur|Raphaël souffle un peu.
+narrateur|Le sachet reste tiède dans ses mains.
+enfant-m|Bonjour.
+enfant-m|Merci.
+papa|Bravo, Raphaël.
+papa|C'est du bon travail.
+narrateur|La cloche reste silencieuse, un moment.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2071,7 +2145,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre la boulangère, le voisin, ou la maîtresse.</t>
+          <t>Trois visages attendent, tout proches. La boulangère, le voisin, ou la maîtresse ? On dit bonjour. On dit merci.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2235,7 +2309,10 @@
       <c r="AV7" s="2" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre la boulangère, le voisin, ou la maîtresse.</t>
+          <t>narrateur|Trois visages attendent, tout proches.
+maman|La boulangère, le voisin, ou la maîtresse ?
+papa|On dit bonjour.
+papa|On dit merci.</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr"/>
@@ -2263,7 +2340,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Corentin dit bonjour. S'il te plaît. Merci.</t>
+          <t>La boulangère a de la farine au tablier. Elle tend un sachet, tout lentement. Bonjour. On dit s'il te plaît. S'il te plaît. Le papier craque, tout doux. Merci. Bravo, Raphaël. Tu as dit les trois mots. On dit bonjour. On dit merci. Un peu de farine colle au sachet. La cloche tinte encore, tout loin. On est encore à la boulangerie. On dit s'il te plaît. On dit merci.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2403,10 +2480,29 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|Corentin dit bonjour. S'il te plaît. Merci.</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr"/>
+          <t>narrateur|La boulangère a de la farine au tablier.
+narrateur|Elle tend un sachet, tout lentement.
+enfant-m|Bonjour.
+maman|On dit s'il te plaît.
+enfant-m|S'il te plaît.
+narrateur|Le papier craque, tout doux.
+enfant-m|Merci.
+papa|Bravo, Raphaël.
+papa|Tu as dit les trois mots.
+maman|On dit bonjour.
+maman|On dit merci.
+narrateur|Un peu de farine colle au sachet.
+narrateur|La cloche tinte encore, tout loin.
+narrateur|On est encore à la boulangerie.
+maman|On dit s'il te plaît.
+maman|On dit merci.</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>papier</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2431,7 +2527,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le pain, une pomme, ou un fromage.</t>
+          <t>Trois choses brillent, dans le panier. Le pain, une pomme, ou un fromage ? On dit encore les mots.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2595,7 +2691,9 @@
       <c r="AV9" s="2" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le pain, une pomme, ou un fromage.</t>
+          <t>narrateur|Trois choses brillent, dans le panier.
+papa|Le pain, une pomme, ou un fromage ?
+maman|On dit encore les mots.</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr"/>
@@ -2623,7 +2721,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Corentin rejoint la boulangère à la boulangerie. Il a le pain. Bonjour, s'il te plaît, merci.</t>
+          <t>Le pain est encore tiède. La croûte fait un petit bruit. Tu veux le pain ? Oui. S'il te plaît. Papa pose le pain dans les mains. Merci, papa. Bravo. Tu as demandé. Puis tu as dit merci. La croûte du pain craque, tout doux. On est encore à la boulangerie. Près de la boulangère. Tu as dit les mots ? Oui. Bonjour. S'il te plaît. Merci. Bravo, Raphaël. Tu as fait du bon travail. Raphaël range le pain, tout doux.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2763,10 +2861,34 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Corentin rejoint la boulangère à la boulangerie. Il a le pain. Bonjour, s'il te plaît, merci.</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr"/>
+          <t>narrateur|Le pain est encore tiède.
+narrateur|La croûte fait un petit bruit.
+papa|Tu veux le pain ?
+enfant-m|Oui.
+enfant-m|S'il te plaît.
+narrateur|Papa pose le pain dans les mains.
+enfant-m|Merci, papa.
+maman|Bravo.
+maman|Tu as demandé.
+maman|Puis tu as dit merci.
+narrateur|La croûte du pain craque, tout doux.
+narrateur|On est encore à la boulangerie.
+narrateur|Près de la boulangère.
+papa|Tu as dit les mots ?
+enfant-m|Oui.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+narrateur|Raphaël range le pain, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2791,7 +2913,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bravo, Raphaël. Tu as dit les trois mots. Raphaël a vécu à la boulangerie. Il a salué la boulangère. Il tient le pain. Le sachet reste tiède, contre le manteau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2931,7 +3053,16 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Raphaël.
+papa|Tu as dit les trois mots.
+narrateur|Raphaël a vécu à la boulangerie.
+narrateur|Il a salué la boulangère.
+narrateur|Il tient le pain.
+narrateur|Le sachet reste tiède, contre le manteau.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr"/>
@@ -2959,7 +3090,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Corentin rejoint la boulangère à la boulangerie. Il a une pomme. Bonjour, s'il te plaît, merci.</t>
+          <t>La pomme est rouge, toute lisse. Un point jaune brille sur la peau. Tu veux la pomme ? S'il te plaît. Maman la pose, tout doux. Merci, maman. Bravo, Raphaël. Tu as dit s'il te plaît. Et merci, maintenant. Merci. La pomme roule près du sachet de farine. On est encore à la boulangerie. Près de la boulangère. Tu as dit les mots ? Oui. Bonjour. S'il te plaît. Merci. Bravo, Raphaël. Tu as fait du bon travail. Raphaël range la pomme, tout doux.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3099,7 +3230,27 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Corentin rejoint la boulangère à la boulangerie. Il a une pomme. Bonjour, s'il te plaît, merci.</t>
+          <t>narrateur|La pomme est rouge, toute lisse.
+narrateur|Un point jaune brille sur la peau.
+maman|Tu veux la pomme ?
+enfant-m|S'il te plaît.
+narrateur|Maman la pose, tout doux.
+enfant-m|Merci, maman.
+papa|Bravo, Raphaël.
+papa|Tu as dit s'il te plaît.
+maman|Et merci, maintenant.
+enfant-m|Merci.
+narrateur|La pomme roule près du sachet de farine.
+narrateur|On est encore à la boulangerie.
+narrateur|Près de la boulangère.
+papa|Tu as dit les mots ?
+enfant-m|Oui.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+narrateur|Raphaël range la pomme, tout doux.</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr"/>
@@ -3127,7 +3278,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bravo, Raphaël. Tu as dit les trois mots. Raphaël a vécu à la boulangerie. Il a salué la boulangère. Il tient la pomme. La pomme garde un point jaune, tout petit. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3267,7 +3418,16 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Raphaël.
+papa|Tu as dit les trois mots.
+narrateur|Raphaël a vécu à la boulangerie.
+narrateur|Il a salué la boulangère.
+narrateur|Il tient la pomme.
+narrateur|La pomme garde un point jaune, tout petit.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr"/>
@@ -3295,7 +3455,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Corentin rejoint la boulangère à la boulangerie. Il a un fromage. Bonjour, s'il te plaît, merci.</t>
+          <t>Le fromage est dans un papier blanc. Le papier fait un bruit doux. On prend le fromage ? Oui. S'il te plaît. Papa tend le paquet, tout lentement. Merci. Bravo. Tu as dit les mots. On dit merci, encore une fois. Merci, papa. Le fromage sent le lait, près du four. On est encore à la boulangerie. Près de la boulangère. Tu as dit les mots ? Oui. Bonjour. S'il te plaît. Merci. Bravo, Raphaël. Tu as fait du bon travail. Raphaël range le fromage, tout doux.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3435,10 +3595,35 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Corentin rejoint la boulangère à la boulangerie. Il a un fromage. Bonjour, s'il te plaît, merci.</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr"/>
+          <t>narrateur|Le fromage est dans un papier blanc.
+narrateur|Le papier fait un bruit doux.
+papa|On prend le fromage ?
+enfant-m|Oui.
+enfant-m|S'il te plaît.
+narrateur|Papa tend le paquet, tout lentement.
+enfant-m|Merci.
+maman|Bravo.
+maman|Tu as dit les mots.
+papa|On dit merci, encore une fois.
+enfant-m|Merci, papa.
+narrateur|Le fromage sent le lait, près du four.
+narrateur|On est encore à la boulangerie.
+narrateur|Près de la boulangère.
+papa|Tu as dit les mots ?
+enfant-m|Oui.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+narrateur|Raphaël range le fromage, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>papier</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3463,7 +3648,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bravo, Raphaël. Tu as dit les trois mots. Raphaël a vécu à la boulangerie. Il a salué la boulangère. Il tient le fromage. Le papier blanc se tait, dans le panier. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3603,7 +3788,16 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Raphaël.
+papa|Tu as dit les trois mots.
+narrateur|Raphaël a vécu à la boulangerie.
+narrateur|Il a salué la boulangère.
+narrateur|Il tient le fromage.
+narrateur|Le papier blanc se tait, dans le panier.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr"/>
@@ -3631,7 +3825,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Corentin dit bonjour. S'il te plaît. Merci.</t>
+          <t>Le voisin tient un panier d'osier. Le panier sent le bois, un peu. On dit bonjour au voisin. Bonjour. Le voisin incline un peu la tête. Tu veux passer ? Oui. S'il te plaît. Raphaël recule, tout doux. Merci. Bravo. Tu as dit les mots. On dit s'il te plaît. On dit merci. Une anse du panier craque, tout petit. Une croûte dore près du panier. On est encore à la boulangerie. On dit s'il te plaît. On dit merci.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3771,7 +3965,25 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Corentin dit bonjour. S'il te plaît. Merci.</t>
+          <t>narrateur|Le voisin tient un panier d'osier.
+narrateur|Le panier sent le bois, un peu.
+papa|On dit bonjour au voisin.
+enfant-m|Bonjour.
+narrateur|Le voisin incline un peu la tête.
+maman|Tu veux passer ?
+enfant-m|Oui.
+enfant-m|S'il te plaît.
+narrateur|Raphaël recule, tout doux.
+enfant-m|Merci.
+papa|Bravo.
+papa|Tu as dit les mots.
+maman|On dit s'il te plaît.
+maman|On dit merci.
+narrateur|Une anse du panier craque, tout petit.
+narrateur|Une croûte dore près du panier.
+narrateur|On est encore à la boulangerie.
+maman|On dit s'il te plaît.
+maman|On dit merci.</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr"/>
@@ -3799,7 +4011,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le pain, une pomme, ou un fromage.</t>
+          <t>Trois choses brillent, dans le panier. Le pain, une pomme, ou un fromage ? On dit encore les mots.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3963,7 +4175,9 @@
       <c r="AV17" s="2" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le pain, une pomme, ou un fromage.</t>
+          <t>narrateur|Trois choses brillent, dans le panier.
+papa|Le pain, une pomme, ou un fromage ?
+maman|On dit encore les mots.</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr"/>
@@ -3991,7 +4205,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Corentin rejoint le voisin à la boulangerie. Il a le pain. Bonjour, s'il te plaît, merci.</t>
+          <t>Le pain est encore tiède. La croûte fait un petit bruit. Tu veux le pain ? Oui. S'il te plaît. Papa pose le pain dans les mains. Merci, papa. Bravo. Tu as demandé. Puis tu as dit merci. Le voisin tient aussi un pain chaud. On est encore à la boulangerie. Près de le voisin. Tu as dit les mots ? Oui. Bonjour. S'il te plaît. Merci. Bravo, Raphaël. Tu as fait du bon travail. Raphaël range le pain, tout doux.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4131,10 +4345,34 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|Corentin rejoint le voisin à la boulangerie. Il a le pain. Bonjour, s'il te plaît, merci.</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr"/>
+          <t>narrateur|Le pain est encore tiède.
+narrateur|La croûte fait un petit bruit.
+papa|Tu veux le pain ?
+enfant-m|Oui.
+enfant-m|S'il te plaît.
+narrateur|Papa pose le pain dans les mains.
+enfant-m|Merci, papa.
+maman|Bravo.
+maman|Tu as demandé.
+maman|Puis tu as dit merci.
+narrateur|Le voisin tient aussi un pain chaud.
+narrateur|On est encore à la boulangerie.
+narrateur|Près de le voisin.
+papa|Tu as dit les mots ?
+enfant-m|Oui.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+narrateur|Raphaël range le pain, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4159,7 +4397,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bravo, Raphaël. Tu as dit les trois mots. Raphaël a vécu à la boulangerie. Il a salué le voisin. Il tient le pain. Le sachet reste tiède, contre le manteau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4299,7 +4537,16 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Raphaël.
+papa|Tu as dit les trois mots.
+narrateur|Raphaël a vécu à la boulangerie.
+narrateur|Il a salué le voisin.
+narrateur|Il tient le pain.
+narrateur|Le sachet reste tiède, contre le manteau.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr"/>
@@ -4327,7 +4574,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Corentin rejoint le voisin à la boulangerie. Il a une pomme. Bonjour, s'il te plaît, merci.</t>
+          <t>La pomme est rouge, toute lisse. Un point jaune brille sur la peau. Tu veux la pomme ? S'il te plaît. Maman la pose, tout doux. Merci, maman. Bravo, Raphaël. Tu as dit s'il te plaît. Et merci, maintenant. Merci. Une miette reste sur la pomme. On est encore à la boulangerie. Près de le voisin. Tu as dit les mots ? Oui. Bonjour. S'il te plaît. Merci. Bravo, Raphaël. Tu as fait du bon travail. Raphaël range la pomme, tout doux.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4467,7 +4714,27 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Corentin rejoint le voisin à la boulangerie. Il a une pomme. Bonjour, s'il te plaît, merci.</t>
+          <t>narrateur|La pomme est rouge, toute lisse.
+narrateur|Un point jaune brille sur la peau.
+maman|Tu veux la pomme ?
+enfant-m|S'il te plaît.
+narrateur|Maman la pose, tout doux.
+enfant-m|Merci, maman.
+papa|Bravo, Raphaël.
+papa|Tu as dit s'il te plaît.
+maman|Et merci, maintenant.
+enfant-m|Merci.
+narrateur|Une miette reste sur la pomme.
+narrateur|On est encore à la boulangerie.
+narrateur|Près de le voisin.
+papa|Tu as dit les mots ?
+enfant-m|Oui.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+narrateur|Raphaël range la pomme, tout doux.</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr"/>
@@ -4495,7 +4762,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bravo, Raphaël. Tu as dit les trois mots. Raphaël a vécu à la boulangerie. Il a salué le voisin. Il tient la pomme. La pomme garde un point jaune, tout petit. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4635,7 +4902,16 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Raphaël.
+papa|Tu as dit les trois mots.
+narrateur|Raphaël a vécu à la boulangerie.
+narrateur|Il a salué le voisin.
+narrateur|Il tient la pomme.
+narrateur|La pomme garde un point jaune, tout petit.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr"/>
@@ -4663,7 +4939,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Corentin rejoint le voisin à la boulangerie. Il a un fromage. Bonjour, s'il te plaît, merci.</t>
+          <t>Le fromage est dans un papier blanc. Le papier fait un bruit doux. On prend le fromage ? Oui. S'il te plaît. Papa tend le paquet, tout lentement. Merci. Bravo. Tu as dit les mots. On dit merci, encore une fois. Merci, papa. Le panier du voisin sent le fromage. On est encore à la boulangerie. Près de le voisin. Tu as dit les mots ? Oui. Bonjour. S'il te plaît. Merci. Bravo, Raphaël. Tu as fait du bon travail. Raphaël range le fromage, tout doux.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4803,10 +5079,35 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|Corentin rejoint le voisin à la boulangerie. Il a un fromage. Bonjour, s'il te plaît, merci.</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr"/>
+          <t>narrateur|Le fromage est dans un papier blanc.
+narrateur|Le papier fait un bruit doux.
+papa|On prend le fromage ?
+enfant-m|Oui.
+enfant-m|S'il te plaît.
+narrateur|Papa tend le paquet, tout lentement.
+enfant-m|Merci.
+maman|Bravo.
+maman|Tu as dit les mots.
+papa|On dit merci, encore une fois.
+enfant-m|Merci, papa.
+narrateur|Le panier du voisin sent le fromage.
+narrateur|On est encore à la boulangerie.
+narrateur|Près de le voisin.
+papa|Tu as dit les mots ?
+enfant-m|Oui.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+narrateur|Raphaël range le fromage, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>papier</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4831,7 +5132,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bravo, Raphaël. Tu as dit les trois mots. Raphaël a vécu à la boulangerie. Il a salué le voisin. Il tient le fromage. Le papier blanc se tait, dans le panier. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -4971,7 +5272,16 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Raphaël.
+papa|Tu as dit les trois mots.
+narrateur|Raphaël a vécu à la boulangerie.
+narrateur|Il a salué le voisin.
+narrateur|Il tient le fromage.
+narrateur|Le papier blanc se tait, dans le panier.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr"/>
@@ -4999,7 +5309,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Corentin dit bonjour. S'il te plaît. Merci.</t>
+          <t>La maîtresse a un sac, tout simple. Bonjour, Raphaël. Bonjour. On dit s'il te plaît. Tu veux saluer encore ? Oui. S'il te plaît. Merci, Raphaël. Merci. Bravo. Tu as dit bonjour. On dit les trois mots. Le sac de la maîtresse sent le pain. De la farine colle au sac d'école. On est encore à la boulangerie. On dit s'il te plaît. On dit merci.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5139,7 +5449,23 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|Corentin dit bonjour. S'il te plaît. Merci.</t>
+          <t>narrateur|La maîtresse a un sac, tout simple.
+maitresse|Bonjour, Raphaël.
+enfant-m|Bonjour.
+maman|On dit s'il te plaît.
+papa|Tu veux saluer encore ?
+enfant-m|Oui.
+enfant-m|S'il te plaît.
+maitresse|Merci, Raphaël.
+enfant-m|Merci.
+papa|Bravo.
+papa|Tu as dit bonjour.
+maman|On dit les trois mots.
+narrateur|Le sac de la maîtresse sent le pain.
+narrateur|De la farine colle au sac d'école.
+narrateur|On est encore à la boulangerie.
+maman|On dit s'il te plaît.
+maman|On dit merci.</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr"/>
@@ -5167,7 +5493,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le pain, une pomme, ou un fromage.</t>
+          <t>Trois choses brillent, dans le panier. Le pain, une pomme, ou un fromage ? On dit encore les mots.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5331,7 +5657,9 @@
       <c r="AV25" s="2" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le pain, une pomme, ou un fromage.</t>
+          <t>narrateur|Trois choses brillent, dans le panier.
+papa|Le pain, une pomme, ou un fromage ?
+maman|On dit encore les mots.</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr"/>
@@ -5359,7 +5687,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Corentin rejoint la maîtresse à la boulangerie. Il a le pain. Bonjour, s'il te plaît, merci.</t>
+          <t>Le pain est encore tiède. La croûte fait un petit bruit. Tu veux le pain ? Oui. S'il te plaît. Papa pose le pain dans les mains. Merci, papa. Bravo. Tu as demandé. Puis tu as dit merci. La maîtresse pose le pain dans son sac. On est encore à la boulangerie. Près de la maîtresse. Tu as dit les mots ? Oui. Bonjour. S'il te plaît. Merci. Bravo, Raphaël. Tu as fait du bon travail. Raphaël range le pain, tout doux.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5499,10 +5827,34 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|Corentin rejoint la maîtresse à la boulangerie. Il a le pain. Bonjour, s'il te plaît, merci.</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr"/>
+          <t>narrateur|Le pain est encore tiède.
+narrateur|La croûte fait un petit bruit.
+papa|Tu veux le pain ?
+enfant-m|Oui.
+enfant-m|S'il te plaît.
+narrateur|Papa pose le pain dans les mains.
+enfant-m|Merci, papa.
+maman|Bravo.
+maman|Tu as demandé.
+maman|Puis tu as dit merci.
+narrateur|La maîtresse pose le pain dans son sac.
+narrateur|On est encore à la boulangerie.
+narrateur|Près de la maîtresse.
+papa|Tu as dit les mots ?
+enfant-m|Oui.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+narrateur|Raphaël range le pain, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5527,7 +5879,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bravo, Raphaël. Tu as dit les trois mots. Raphaël a vécu à la boulangerie. Il a salué la maîtresse. Il tient le pain. Le sachet reste tiède, contre le manteau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5667,7 +6019,16 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Raphaël.
+papa|Tu as dit les trois mots.
+narrateur|Raphaël a vécu à la boulangerie.
+narrateur|Il a salué la maîtresse.
+narrateur|Il tient le pain.
+narrateur|Le sachet reste tiède, contre le manteau.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr"/>
@@ -5695,7 +6056,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Corentin rejoint la maîtresse à la boulangerie. Il a une pomme. Bonjour, s'il te plaît, merci.</t>
+          <t>La pomme est rouge, toute lisse. Un point jaune brille sur la peau. Tu veux la pomme ? S'il te plaît. Maman la pose, tout doux. Merci, maman. Bravo, Raphaël. Tu as dit s'il te plaît. Et merci, maintenant. Merci. La maîtresse essuie la pomme, tout doux. On est encore à la boulangerie. Près de la maîtresse. Tu as dit les mots ? Oui. Bonjour. S'il te plaît. Merci. Bravo, Raphaël. Tu as fait du bon travail. Raphaël range la pomme, tout doux.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5835,7 +6196,27 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|Corentin rejoint la maîtresse à la boulangerie. Il a une pomme. Bonjour, s'il te plaît, merci.</t>
+          <t>narrateur|La pomme est rouge, toute lisse.
+narrateur|Un point jaune brille sur la peau.
+maman|Tu veux la pomme ?
+enfant-m|S'il te plaît.
+narrateur|Maman la pose, tout doux.
+enfant-m|Merci, maman.
+papa|Bravo, Raphaël.
+papa|Tu as dit s'il te plaît.
+maman|Et merci, maintenant.
+enfant-m|Merci.
+narrateur|La maîtresse essuie la pomme, tout doux.
+narrateur|On est encore à la boulangerie.
+narrateur|Près de la maîtresse.
+papa|Tu as dit les mots ?
+enfant-m|Oui.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+narrateur|Raphaël range la pomme, tout doux.</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr"/>
@@ -5863,7 +6244,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bravo, Raphaël. Tu as dit les trois mots. Raphaël a vécu à la boulangerie. Il a salué la maîtresse. Il tient la pomme. La pomme garde un point jaune, tout petit. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6003,7 +6384,16 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Raphaël.
+papa|Tu as dit les trois mots.
+narrateur|Raphaël a vécu à la boulangerie.
+narrateur|Il a salué la maîtresse.
+narrateur|Il tient la pomme.
+narrateur|La pomme garde un point jaune, tout petit.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr"/>
@@ -6031,7 +6421,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Corentin rejoint la maîtresse à la boulangerie. Il a un fromage. Bonjour, s'il te plaît, merci.</t>
+          <t>Le fromage est dans un papier blanc. Le papier fait un bruit doux. On prend le fromage ? Oui. S'il te plaît. Papa tend le paquet, tout lentement. Merci. Bravo. Tu as dit les mots. On dit merci, encore une fois. Merci, papa. Le fromage glisse dans le sac. On est encore à la boulangerie. Près de la maîtresse. Tu as dit les mots ? Oui. Bonjour. S'il te plaît. Merci. Bravo, Raphaël. Tu as fait du bon travail. Raphaël range le fromage, tout doux.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6171,10 +6561,35 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|Corentin rejoint la maîtresse à la boulangerie. Il a un fromage. Bonjour, s'il te plaît, merci.</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr"/>
+          <t>narrateur|Le fromage est dans un papier blanc.
+narrateur|Le papier fait un bruit doux.
+papa|On prend le fromage ?
+enfant-m|Oui.
+enfant-m|S'il te plaît.
+narrateur|Papa tend le paquet, tout lentement.
+enfant-m|Merci.
+maman|Bravo.
+maman|Tu as dit les mots.
+papa|On dit merci, encore une fois.
+enfant-m|Merci, papa.
+narrateur|Le fromage glisse dans le sac.
+narrateur|On est encore à la boulangerie.
+narrateur|Près de la maîtresse.
+papa|Tu as dit les mots ?
+enfant-m|Oui.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+narrateur|Raphaël range le fromage, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>papier</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6199,7 +6614,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bravo, Raphaël. Tu as dit les trois mots. Raphaël a vécu à la boulangerie. Il a salué la maîtresse. Il tient le fromage. Le papier blanc se tait, dans le panier. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6339,7 +6754,16 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Raphaël.
+papa|Tu as dit les trois mots.
+narrateur|Raphaël a vécu à la boulangerie.
+narrateur|Il a salué la maîtresse.
+narrateur|Il tient le fromage.
+narrateur|Le papier blanc se tait, dans le panier.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr"/>
@@ -6367,7 +6791,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>À l'étal, Corentin dit bonjour. S'il te plaît. Merci.</t>
+          <t>Raphaël s'arrête devant l'étal. Les caisses sentent le bois mouillé. Des pommes rouges brillent, tout près. Un papier vert frissonne au vent. Un pigeon picore encore une miette. On dit bonjour, ici aussi. Bonjour. Bonjour. Tu veux une pomme ? Oui. S'il te plaît. Maman pose une pomme dans sa main. La peau est lisse, un peu froide. Merci. Bravo. Tu as dit s'il te plaît. Tu as dit merci. On dit les mots, à l'étal. Une feuille verte colle à une caisse.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6507,10 +6931,32 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|À l'étal, Corentin dit bonjour. S'il te plaît. Merci.</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr"/>
+          <t>narrateur|Raphaël s'arrête devant l'étal.
+narrateur|Les caisses sentent le bois mouillé.
+narrateur|Des pommes rouges brillent, tout près.
+narrateur|Un papier vert frissonne au vent.
+narrateur|Un pigeon picore encore une miette.
+maman|On dit bonjour, ici aussi.
+enfant-m|Bonjour.
+papa|Bonjour.
+papa|Tu veux une pomme ?
+enfant-m|Oui.
+enfant-m|S'il te plaît.
+narrateur|Maman pose une pomme dans sa main.
+narrateur|La peau est lisse, un peu froide.
+enfant-m|Merci.
+maman|Bravo.
+maman|Tu as dit s'il te plaît.
+maman|Tu as dit merci.
+papa|On dit les mots, à l'étal.
+narrateur|Une feuille verte colle à une caisse.</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6535,7 +6981,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>À l'étal, quels mots ?</t>
+          <t>À l'étal, Raphaël demande. Quels mots ?</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -6691,7 +7137,8 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>narrateur|À l'étal, quels mots ?</t>
+          <t>narrateur|À l'étal, Raphaël demande.
+papa|Quels mots ?</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr"/>
@@ -6719,7 +7166,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. Les trois mots.</t>
+          <t>Oui. On dit s'il te plaît. On dit merci. Raphaël serre la pomme, tout doux. S'il te plaît. Merci. Bravo. Tu as dit les mots. Le pigeon s'envole, tout près des caisses.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6859,7 +7306,15 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Les trois mots.</t>
+          <t>papa|Oui.
+papa|On dit s'il te plaît.
+papa|On dit merci.
+narrateur|Raphaël serre la pomme, tout doux.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo.
+maman|Tu as dit les mots.
+narrateur|Le pigeon s'envole, tout près des caisses.</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr"/>
@@ -6887,7 +7342,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre la boulangère, le voisin, ou la maîtresse.</t>
+          <t>Trois visages attendent, tout proches. La boulangère, le voisin, ou la maîtresse ? On dit bonjour. On dit merci.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -7051,7 +7506,10 @@
       <c r="AV35" s="2" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre la boulangère, le voisin, ou la maîtresse.</t>
+          <t>narrateur|Trois visages attendent, tout proches.
+maman|La boulangère, le voisin, ou la maîtresse ?
+papa|On dit bonjour.
+papa|On dit merci.</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr"/>
@@ -7079,7 +7537,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Corentin dit bonjour. S'il te plaît. Merci.</t>
+          <t>La boulangère a de la farine au tablier. Elle tend un sachet, tout lentement. Bonjour. On dit s'il te plaît. S'il te plaît. Le papier craque, tout doux. Merci. Bravo, Raphaël. Tu as dit les trois mots. On dit bonjour. On dit merci. Un peu de farine colle au sachet. Une pomme rouge roule près du tablier. On est encore à l'étal. On dit s'il te plaît. On dit merci.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7219,10 +7677,29 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|Corentin dit bonjour. S'il te plaît. Merci.</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr"/>
+          <t>narrateur|La boulangère a de la farine au tablier.
+narrateur|Elle tend un sachet, tout lentement.
+enfant-m|Bonjour.
+maman|On dit s'il te plaît.
+enfant-m|S'il te plaît.
+narrateur|Le papier craque, tout doux.
+enfant-m|Merci.
+papa|Bravo, Raphaël.
+papa|Tu as dit les trois mots.
+maman|On dit bonjour.
+maman|On dit merci.
+narrateur|Un peu de farine colle au sachet.
+narrateur|Une pomme rouge roule près du tablier.
+narrateur|On est encore à l'étal.
+maman|On dit s'il te plaît.
+maman|On dit merci.</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>papier</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7247,7 +7724,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le pain, une pomme, ou un fromage.</t>
+          <t>Trois choses brillent, dans le panier. Le pain, une pomme, ou un fromage ? On dit encore les mots.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7411,7 +7888,9 @@
       <c r="AV37" s="2" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le pain, une pomme, ou un fromage.</t>
+          <t>narrateur|Trois choses brillent, dans le panier.
+papa|Le pain, une pomme, ou un fromage ?
+maman|On dit encore les mots.</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr"/>
@@ -7439,7 +7918,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Corentin rejoint la boulangère à l'étal. Il a le pain. Bonjour, s'il te plaît, merci.</t>
+          <t>Le pain est encore tiède. La croûte fait un petit bruit. Tu veux le pain ? Oui. S'il te plaît. Papa pose le pain dans les mains. Merci, papa. Bravo. Tu as demandé. Puis tu as dit merci. La boulangère a le pain, à l'étal. On est encore à l'étal. Près de la boulangère. Tu as dit les mots ? Oui. Bonjour. S'il te plaît. Merci. Bravo, Raphaël. Tu as fait du bon travail. Raphaël range le pain, tout doux.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7579,10 +8058,34 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Corentin rejoint la boulangère à l'étal. Il a le pain. Bonjour, s'il te plaît, merci.</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr"/>
+          <t>narrateur|Le pain est encore tiède.
+narrateur|La croûte fait un petit bruit.
+papa|Tu veux le pain ?
+enfant-m|Oui.
+enfant-m|S'il te plaît.
+narrateur|Papa pose le pain dans les mains.
+enfant-m|Merci, papa.
+maman|Bravo.
+maman|Tu as demandé.
+maman|Puis tu as dit merci.
+narrateur|La boulangère a le pain, à l'étal.
+narrateur|On est encore à l'étal.
+narrateur|Près de la boulangère.
+papa|Tu as dit les mots ?
+enfant-m|Oui.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+narrateur|Raphaël range le pain, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7607,7 +8110,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bravo, Raphaël. Tu as dit les trois mots. Raphaël a vécu à l'étal. Il a salué la boulangère. Il tient le pain. Le sachet reste tiède, contre le manteau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7747,7 +8250,16 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Raphaël.
+papa|Tu as dit les trois mots.
+narrateur|Raphaël a vécu à l'étal.
+narrateur|Il a salué la boulangère.
+narrateur|Il tient le pain.
+narrateur|Le sachet reste tiède, contre le manteau.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr"/>
@@ -7775,7 +8287,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Corentin rejoint la boulangère à l'étal. Il a une pomme. Bonjour, s'il te plaît, merci.</t>
+          <t>La pomme est rouge, toute lisse. Un point jaune brille sur la peau. Tu veux la pomme ? S'il te plaît. Maman la pose, tout doux. Merci, maman. Bravo, Raphaël. Tu as dit s'il te plaît. Et merci, maintenant. Merci. La boulangère choisit une pomme rouge. On est encore à l'étal. Près de la boulangère. Tu as dit les mots ? Oui. Bonjour. S'il te plaît. Merci. Bravo, Raphaël. Tu as fait du bon travail. Raphaël range la pomme, tout doux.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7915,7 +8427,27 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Corentin rejoint la boulangère à l'étal. Il a une pomme. Bonjour, s'il te plaît, merci.</t>
+          <t>narrateur|La pomme est rouge, toute lisse.
+narrateur|Un point jaune brille sur la peau.
+maman|Tu veux la pomme ?
+enfant-m|S'il te plaît.
+narrateur|Maman la pose, tout doux.
+enfant-m|Merci, maman.
+papa|Bravo, Raphaël.
+papa|Tu as dit s'il te plaît.
+maman|Et merci, maintenant.
+enfant-m|Merci.
+narrateur|La boulangère choisit une pomme rouge.
+narrateur|On est encore à l'étal.
+narrateur|Près de la boulangère.
+papa|Tu as dit les mots ?
+enfant-m|Oui.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+narrateur|Raphaël range la pomme, tout doux.</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr"/>
@@ -7943,7 +8475,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bravo, Raphaël. Tu as dit les trois mots. Raphaël a vécu à l'étal. Il a salué la boulangère. Il tient la pomme. La pomme garde un point jaune, tout petit. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8083,7 +8615,16 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Raphaël.
+papa|Tu as dit les trois mots.
+narrateur|Raphaël a vécu à l'étal.
+narrateur|Il a salué la boulangère.
+narrateur|Il tient la pomme.
+narrateur|La pomme garde un point jaune, tout petit.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr"/>
@@ -8111,7 +8652,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Corentin rejoint la boulangère à l'étal. Il a un fromage. Bonjour, s'il te plaît, merci.</t>
+          <t>Le fromage est dans un papier blanc. Le papier fait un bruit doux. On prend le fromage ? Oui. S'il te plaît. Papa tend le paquet, tout lentement. Merci. Bravo. Tu as dit les mots. On dit merci, encore une fois. Merci, papa. Un papier blanc entoure le fromage. On est encore à l'étal. Près de la boulangère. Tu as dit les mots ? Oui. Bonjour. S'il te plaît. Merci. Bravo, Raphaël. Tu as fait du bon travail. Raphaël range le fromage, tout doux.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8251,10 +8792,35 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Corentin rejoint la boulangère à l'étal. Il a un fromage. Bonjour, s'il te plaît, merci.</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr"/>
+          <t>narrateur|Le fromage est dans un papier blanc.
+narrateur|Le papier fait un bruit doux.
+papa|On prend le fromage ?
+enfant-m|Oui.
+enfant-m|S'il te plaît.
+narrateur|Papa tend le paquet, tout lentement.
+enfant-m|Merci.
+maman|Bravo.
+maman|Tu as dit les mots.
+papa|On dit merci, encore une fois.
+enfant-m|Merci, papa.
+narrateur|Un papier blanc entoure le fromage.
+narrateur|On est encore à l'étal.
+narrateur|Près de la boulangère.
+papa|Tu as dit les mots ?
+enfant-m|Oui.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+narrateur|Raphaël range le fromage, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>papier</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8279,7 +8845,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bravo, Raphaël. Tu as dit les trois mots. Raphaël a vécu à l'étal. Il a salué la boulangère. Il tient le fromage. Le papier blanc se tait, dans le panier. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8419,7 +8985,16 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Raphaël.
+papa|Tu as dit les trois mots.
+narrateur|Raphaël a vécu à l'étal.
+narrateur|Il a salué la boulangère.
+narrateur|Il tient le fromage.
+narrateur|Le papier blanc se tait, dans le panier.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr"/>
@@ -8447,7 +9022,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Corentin dit bonjour. S'il te plaît. Merci.</t>
+          <t>Le voisin tient un panier d'osier. Le panier sent le bois, un peu. On dit bonjour au voisin. Bonjour. Le voisin incline un peu la tête. Tu veux passer ? Oui. S'il te plaît. Raphaël recule, tout doux. Merci. Bravo. Tu as dit les mots. On dit s'il te plaît. On dit merci. Une anse du panier craque, tout petit. Le pigeon revient, près des caisses. On est encore à l'étal. On dit s'il te plaît. On dit merci.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8587,7 +9162,25 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Corentin dit bonjour. S'il te plaît. Merci.</t>
+          <t>narrateur|Le voisin tient un panier d'osier.
+narrateur|Le panier sent le bois, un peu.
+papa|On dit bonjour au voisin.
+enfant-m|Bonjour.
+narrateur|Le voisin incline un peu la tête.
+maman|Tu veux passer ?
+enfant-m|Oui.
+enfant-m|S'il te plaît.
+narrateur|Raphaël recule, tout doux.
+enfant-m|Merci.
+papa|Bravo.
+papa|Tu as dit les mots.
+maman|On dit s'il te plaît.
+maman|On dit merci.
+narrateur|Une anse du panier craque, tout petit.
+narrateur|Le pigeon revient, près des caisses.
+narrateur|On est encore à l'étal.
+maman|On dit s'il te plaît.
+maman|On dit merci.</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr"/>
@@ -8615,7 +9208,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le pain, une pomme, ou un fromage.</t>
+          <t>Trois choses brillent, dans le panier. Le pain, une pomme, ou un fromage ? On dit encore les mots.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -8779,7 +9372,9 @@
       <c r="AV45" s="2" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le pain, une pomme, ou un fromage.</t>
+          <t>narrateur|Trois choses brillent, dans le panier.
+papa|Le pain, une pomme, ou un fromage ?
+maman|On dit encore les mots.</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr"/>
@@ -8807,7 +9402,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Corentin rejoint le voisin à l'étal. Il a le pain. Bonjour, s'il te plaît, merci.</t>
+          <t>Le pain est encore tiède. La croûte fait un petit bruit. Tu veux le pain ? Oui. S'il te plaît. Papa pose le pain dans les mains. Merci, papa. Bravo. Tu as demandé. Puis tu as dit merci. Le voisin pose le pain sur la caisse. On est encore à l'étal. Près de le voisin. Tu as dit les mots ? Oui. Bonjour. S'il te plaît. Merci. Bravo, Raphaël. Tu as fait du bon travail. Raphaël range le pain, tout doux.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8947,10 +9542,34 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|Corentin rejoint le voisin à l'étal. Il a le pain. Bonjour, s'il te plaît, merci.</t>
-        </is>
-      </c>
-      <c r="AX46" t="inlineStr"/>
+          <t>narrateur|Le pain est encore tiède.
+narrateur|La croûte fait un petit bruit.
+papa|Tu veux le pain ?
+enfant-m|Oui.
+enfant-m|S'il te plaît.
+narrateur|Papa pose le pain dans les mains.
+enfant-m|Merci, papa.
+maman|Bravo.
+maman|Tu as demandé.
+maman|Puis tu as dit merci.
+narrateur|Le voisin pose le pain sur la caisse.
+narrateur|On est encore à l'étal.
+narrateur|Près de le voisin.
+papa|Tu as dit les mots ?
+enfant-m|Oui.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+narrateur|Raphaël range le pain, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8975,7 +9594,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bravo, Raphaël. Tu as dit les trois mots. Raphaël a vécu à l'étal. Il a salué le voisin. Il tient le pain. Le sachet reste tiède, contre le manteau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9115,7 +9734,16 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Raphaël.
+papa|Tu as dit les trois mots.
+narrateur|Raphaël a vécu à l'étal.
+narrateur|Il a salué le voisin.
+narrateur|Il tient le pain.
+narrateur|Le sachet reste tiède, contre le manteau.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr"/>
@@ -9143,7 +9771,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Corentin rejoint le voisin à l'étal. Il a une pomme. Bonjour, s'il te plaît, merci.</t>
+          <t>La pomme est rouge, toute lisse. Un point jaune brille sur la peau. Tu veux la pomme ? S'il te plaît. Maman la pose, tout doux. Merci, maman. Bravo, Raphaël. Tu as dit s'il te plaît. Et merci, maintenant. Merci. Deux pommes se touchent, dans le panier. On est encore à l'étal. Près de le voisin. Tu as dit les mots ? Oui. Bonjour. S'il te plaît. Merci. Bravo, Raphaël. Tu as fait du bon travail. Raphaël range la pomme, tout doux.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9283,7 +9911,27 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|Corentin rejoint le voisin à l'étal. Il a une pomme. Bonjour, s'il te plaît, merci.</t>
+          <t>narrateur|La pomme est rouge, toute lisse.
+narrateur|Un point jaune brille sur la peau.
+maman|Tu veux la pomme ?
+enfant-m|S'il te plaît.
+narrateur|Maman la pose, tout doux.
+enfant-m|Merci, maman.
+papa|Bravo, Raphaël.
+papa|Tu as dit s'il te plaît.
+maman|Et merci, maintenant.
+enfant-m|Merci.
+narrateur|Deux pommes se touchent, dans le panier.
+narrateur|On est encore à l'étal.
+narrateur|Près de le voisin.
+papa|Tu as dit les mots ?
+enfant-m|Oui.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+narrateur|Raphaël range la pomme, tout doux.</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr"/>
@@ -9311,7 +9959,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bravo, Raphaël. Tu as dit les trois mots. Raphaël a vécu à l'étal. Il a salué le voisin. Il tient la pomme. La pomme garde un point jaune, tout petit. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9451,7 +10099,16 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Raphaël.
+papa|Tu as dit les trois mots.
+narrateur|Raphaël a vécu à l'étal.
+narrateur|Il a salué le voisin.
+narrateur|Il tient la pomme.
+narrateur|La pomme garde un point jaune, tout petit.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr"/>
@@ -9479,7 +10136,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Corentin rejoint le voisin à l'étal. Il a un fromage. Bonjour, s'il te plaît, merci.</t>
+          <t>Le fromage est dans un papier blanc. Le papier fait un bruit doux. On prend le fromage ? Oui. S'il te plaît. Papa tend le paquet, tout lentement. Merci. Bravo. Tu as dit les mots. On dit merci, encore une fois. Merci, papa. Le fromage pèse un peu, dans les mains. On est encore à l'étal. Près de le voisin. Tu as dit les mots ? Oui. Bonjour. S'il te plaît. Merci. Bravo, Raphaël. Tu as fait du bon travail. Raphaël range le fromage, tout doux.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9619,10 +10276,35 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|Corentin rejoint le voisin à l'étal. Il a un fromage. Bonjour, s'il te plaît, merci.</t>
-        </is>
-      </c>
-      <c r="AX50" t="inlineStr"/>
+          <t>narrateur|Le fromage est dans un papier blanc.
+narrateur|Le papier fait un bruit doux.
+papa|On prend le fromage ?
+enfant-m|Oui.
+enfant-m|S'il te plaît.
+narrateur|Papa tend le paquet, tout lentement.
+enfant-m|Merci.
+maman|Bravo.
+maman|Tu as dit les mots.
+papa|On dit merci, encore une fois.
+enfant-m|Merci, papa.
+narrateur|Le fromage pèse un peu, dans les mains.
+narrateur|On est encore à l'étal.
+narrateur|Près de le voisin.
+papa|Tu as dit les mots ?
+enfant-m|Oui.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+narrateur|Raphaël range le fromage, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>papier</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9647,7 +10329,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bravo, Raphaël. Tu as dit les trois mots. Raphaël a vécu à l'étal. Il a salué le voisin. Il tient le fromage. Le papier blanc se tait, dans le panier. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9787,7 +10469,16 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Raphaël.
+papa|Tu as dit les trois mots.
+narrateur|Raphaël a vécu à l'étal.
+narrateur|Il a salué le voisin.
+narrateur|Il tient le fromage.
+narrateur|Le papier blanc se tait, dans le panier.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr"/>
@@ -9815,7 +10506,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Corentin dit bonjour. S'il te plaît. Merci.</t>
+          <t>La maîtresse a un sac, tout simple. Bonjour, Raphaël. Bonjour. On dit s'il te plaît. Tu veux saluer encore ? Oui. S'il te plaît. Merci, Raphaël. Merci. Bravo. Tu as dit bonjour. On dit les trois mots. Le sac de la maîtresse sent le pain. Le papier vert frôle le sac. On est encore à l'étal. On dit s'il te plaît. On dit merci.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9955,7 +10646,23 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Corentin dit bonjour. S'il te plaît. Merci.</t>
+          <t>narrateur|La maîtresse a un sac, tout simple.
+maitresse|Bonjour, Raphaël.
+enfant-m|Bonjour.
+maman|On dit s'il te plaît.
+papa|Tu veux saluer encore ?
+enfant-m|Oui.
+enfant-m|S'il te plaît.
+maitresse|Merci, Raphaël.
+enfant-m|Merci.
+papa|Bravo.
+papa|Tu as dit bonjour.
+maman|On dit les trois mots.
+narrateur|Le sac de la maîtresse sent le pain.
+narrateur|Le papier vert frôle le sac.
+narrateur|On est encore à l'étal.
+maman|On dit s'il te plaît.
+maman|On dit merci.</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr"/>
@@ -9983,7 +10690,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le pain, une pomme, ou un fromage.</t>
+          <t>Trois choses brillent, dans le panier. Le pain, une pomme, ou un fromage ? On dit encore les mots.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10147,7 +10854,9 @@
       <c r="AV53" s="2" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le pain, une pomme, ou un fromage.</t>
+          <t>narrateur|Trois choses brillent, dans le panier.
+papa|Le pain, une pomme, ou un fromage ?
+maman|On dit encore les mots.</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr"/>
@@ -10175,7 +10884,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Corentin rejoint la maîtresse à l'étal. Il a le pain. Bonjour, s'il te plaît, merci.</t>
+          <t>Le pain est encore tiède. La croûte fait un petit bruit. Tu veux le pain ? Oui. S'il te plaît. Papa pose le pain dans les mains. Merci, papa. Bravo. Tu as demandé. Puis tu as dit merci. La maîtresse sent le pain, tout près. On est encore à l'étal. Près de la maîtresse. Tu as dit les mots ? Oui. Bonjour. S'il te plaît. Merci. Bravo, Raphaël. Tu as fait du bon travail. Raphaël range le pain, tout doux.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10315,10 +11024,34 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|Corentin rejoint la maîtresse à l'étal. Il a le pain. Bonjour, s'il te plaît, merci.</t>
-        </is>
-      </c>
-      <c r="AX54" t="inlineStr"/>
+          <t>narrateur|Le pain est encore tiède.
+narrateur|La croûte fait un petit bruit.
+papa|Tu veux le pain ?
+enfant-m|Oui.
+enfant-m|S'il te plaît.
+narrateur|Papa pose le pain dans les mains.
+enfant-m|Merci, papa.
+maman|Bravo.
+maman|Tu as demandé.
+maman|Puis tu as dit merci.
+narrateur|La maîtresse sent le pain, tout près.
+narrateur|On est encore à l'étal.
+narrateur|Près de la maîtresse.
+papa|Tu as dit les mots ?
+enfant-m|Oui.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+narrateur|Raphaël range le pain, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10343,7 +11076,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bravo, Raphaël. Tu as dit les trois mots. Raphaël a vécu à l'étal. Il a salué la maîtresse. Il tient le pain. Le sachet reste tiède, contre le manteau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10483,7 +11216,16 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Raphaël.
+papa|Tu as dit les trois mots.
+narrateur|Raphaël a vécu à l'étal.
+narrateur|Il a salué la maîtresse.
+narrateur|Il tient le pain.
+narrateur|Le sachet reste tiède, contre le manteau.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr"/>
@@ -10511,7 +11253,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Corentin rejoint la maîtresse à l'étal. Il a une pomme. Bonjour, s'il te plaît, merci.</t>
+          <t>La pomme est rouge, toute lisse. Un point jaune brille sur la peau. Tu veux la pomme ? S'il te plaît. Maman la pose, tout doux. Merci, maman. Bravo, Raphaël. Tu as dit s'il te plaît. Et merci, maintenant. Merci. Une feuille verte colle à la pomme. On est encore à l'étal. Près de la maîtresse. Tu as dit les mots ? Oui. Bonjour. S'il te plaît. Merci. Bravo, Raphaël. Tu as fait du bon travail. Raphaël range la pomme, tout doux.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10651,7 +11393,27 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|Corentin rejoint la maîtresse à l'étal. Il a une pomme. Bonjour, s'il te plaît, merci.</t>
+          <t>narrateur|La pomme est rouge, toute lisse.
+narrateur|Un point jaune brille sur la peau.
+maman|Tu veux la pomme ?
+enfant-m|S'il te plaît.
+narrateur|Maman la pose, tout doux.
+enfant-m|Merci, maman.
+papa|Bravo, Raphaël.
+papa|Tu as dit s'il te plaît.
+maman|Et merci, maintenant.
+enfant-m|Merci.
+narrateur|Une feuille verte colle à la pomme.
+narrateur|On est encore à l'étal.
+narrateur|Près de la maîtresse.
+papa|Tu as dit les mots ?
+enfant-m|Oui.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+narrateur|Raphaël range la pomme, tout doux.</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr"/>
@@ -10679,7 +11441,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bravo, Raphaël. Tu as dit les trois mots. Raphaël a vécu à l'étal. Il a salué la maîtresse. Il tient la pomme. La pomme garde un point jaune, tout petit. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10819,7 +11581,16 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Raphaël.
+papa|Tu as dit les trois mots.
+narrateur|Raphaël a vécu à l'étal.
+narrateur|Il a salué la maîtresse.
+narrateur|Il tient la pomme.
+narrateur|La pomme garde un point jaune, tout petit.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr"/>
@@ -10847,7 +11618,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Corentin rejoint la maîtresse à l'étal. Il a un fromage. Bonjour, s'il te plaît, merci.</t>
+          <t>Le fromage est dans un papier blanc. Le papier fait un bruit doux. On prend le fromage ? Oui. S'il te plaît. Papa tend le paquet, tout lentement. Merci. Bravo. Tu as dit les mots. On dit merci, encore une fois. Merci, papa. Le fromage reste frais, sous le store. On est encore à l'étal. Près de la maîtresse. Tu as dit les mots ? Oui. Bonjour. S'il te plaît. Merci. Bravo, Raphaël. Tu as fait du bon travail. Raphaël range le fromage, tout doux.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -10987,10 +11758,35 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Corentin rejoint la maîtresse à l'étal. Il a un fromage. Bonjour, s'il te plaît, merci.</t>
-        </is>
-      </c>
-      <c r="AX58" t="inlineStr"/>
+          <t>narrateur|Le fromage est dans un papier blanc.
+narrateur|Le papier fait un bruit doux.
+papa|On prend le fromage ?
+enfant-m|Oui.
+enfant-m|S'il te plaît.
+narrateur|Papa tend le paquet, tout lentement.
+enfant-m|Merci.
+maman|Bravo.
+maman|Tu as dit les mots.
+papa|On dit merci, encore une fois.
+enfant-m|Merci, papa.
+narrateur|Le fromage reste frais, sous le store.
+narrateur|On est encore à l'étal.
+narrateur|Près de la maîtresse.
+papa|Tu as dit les mots ?
+enfant-m|Oui.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+narrateur|Raphaël range le fromage, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>papier</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11015,7 +11811,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bravo, Raphaël. Tu as dit les trois mots. Raphaël a vécu à l'étal. Il a salué la maîtresse. Il tient le fromage. Le papier blanc se tait, dans le panier. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11155,7 +11951,16 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Raphaël.
+papa|Tu as dit les trois mots.
+narrateur|Raphaël a vécu à l'étal.
+narrateur|Il a salué la maîtresse.
+narrateur|Il tient le fromage.
+narrateur|Le papier blanc se tait, dans le panier.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr"/>
@@ -11183,7 +11988,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>À la fromagerie, Corentin dit bonjour. S'il te plaît. Merci.</t>
+          <t>Raphaël entre dans la fromagerie. L'air est frais, tout calme. Le comptoir de marbre est froid. Ça sent le lait, tout doux. Un papier blanc attend, tout plié. On dit bonjour. Bonjour. Bonjour. Tu veux goûter l'odeur ? Oui. S'il te plaît. Papa approche le papier, tout lentement. Merci, papa. Bravo, Raphaël. Tu as dit les mots. On dit s'il te plaît. On dit merci. Une goutte d'eau brille sur le marbre.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11323,7 +12128,24 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|À la fromagerie, Corentin dit bonjour. S'il te plaît. Merci.</t>
+          <t>narrateur|Raphaël entre dans la fromagerie.
+narrateur|L'air est frais, tout calme.
+narrateur|Le comptoir de marbre est froid.
+narrateur|Ça sent le lait, tout doux.
+narrateur|Un papier blanc attend, tout plié.
+papa|On dit bonjour.
+enfant-m|Bonjour.
+maman|Bonjour.
+maman|Tu veux goûter l'odeur ?
+enfant-m|Oui.
+enfant-m|S'il te plaît.
+narrateur|Papa approche le papier, tout lentement.
+enfant-m|Merci, papa.
+papa|Bravo, Raphaël.
+papa|Tu as dit les mots.
+maman|On dit s'il te plaît.
+maman|On dit merci.
+narrateur|Une goutte d'eau brille sur le marbre.</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr"/>
@@ -11351,7 +12173,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>À la fromagerie, quels mots ?</t>
+          <t>Dans la fromagerie, on salue. Raphaël dit merci ?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -11507,7 +12329,8 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>narrateur|À la fromagerie, quels mots ?</t>
+          <t>narrateur|Dans la fromagerie, on salue.
+maman|Raphaël dit merci ?</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr"/>
@@ -11535,7 +12358,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Corentin a salué.</t>
+          <t>Oui. On dit bonjour. On dit merci. Raphaël touche le papier, tout léger. Merci. Bravo. Tu as salué. Et tu as demandé, tout doux. Le marbre reste froid, tout calme.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11675,7 +12498,15 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Corentin a salué.</t>
+          <t>maman|Oui.
+maman|On dit bonjour.
+maman|On dit merci.
+narrateur|Raphaël touche le papier, tout léger.
+enfant-m|Merci.
+papa|Bravo.
+papa|Tu as salué.
+maman|Et tu as demandé, tout doux.
+narrateur|Le marbre reste froid, tout calme.</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr"/>
@@ -11703,7 +12534,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre la boulangère, le voisin, ou la maîtresse.</t>
+          <t>Trois visages attendent, tout proches. La boulangère, le voisin, ou la maîtresse ? On dit bonjour. On dit merci.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -11867,7 +12698,10 @@
       <c r="AV63" s="2" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre la boulangère, le voisin, ou la maîtresse.</t>
+          <t>narrateur|Trois visages attendent, tout proches.
+maman|La boulangère, le voisin, ou la maîtresse ?
+papa|On dit bonjour.
+papa|On dit merci.</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr"/>
@@ -11895,7 +12729,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Corentin dit bonjour. S'il te plaît. Merci.</t>
+          <t>La boulangère a de la farine au tablier. Elle tend un sachet, tout lentement. Bonjour. On dit s'il te plaît. S'il te plaît. Le papier craque, tout doux. Merci. Bravo, Raphaël. Tu as dit les trois mots. On dit bonjour. On dit merci. Un peu de farine colle au sachet. Le marbre refroidit encore le sachet. On est encore à la fromagerie. On dit s'il te plaît. On dit merci.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12035,10 +12869,29 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Corentin dit bonjour. S'il te plaît. Merci.</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr"/>
+          <t>narrateur|La boulangère a de la farine au tablier.
+narrateur|Elle tend un sachet, tout lentement.
+enfant-m|Bonjour.
+maman|On dit s'il te plaît.
+enfant-m|S'il te plaît.
+narrateur|Le papier craque, tout doux.
+enfant-m|Merci.
+papa|Bravo, Raphaël.
+papa|Tu as dit les trois mots.
+maman|On dit bonjour.
+maman|On dit merci.
+narrateur|Un peu de farine colle au sachet.
+narrateur|Le marbre refroidit encore le sachet.
+narrateur|On est encore à la fromagerie.
+maman|On dit s'il te plaît.
+maman|On dit merci.</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>papier</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12063,7 +12916,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le pain, une pomme, ou un fromage.</t>
+          <t>Trois choses brillent, dans le panier. Le pain, une pomme, ou un fromage ? On dit encore les mots.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12227,7 +13080,9 @@
       <c r="AV65" s="2" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le pain, une pomme, ou un fromage.</t>
+          <t>narrateur|Trois choses brillent, dans le panier.
+papa|Le pain, une pomme, ou un fromage ?
+maman|On dit encore les mots.</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr"/>
@@ -12255,7 +13110,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Corentin rejoint la boulangère à la fromagerie. Il a le pain. Bonjour, s'il te plaît, merci.</t>
+          <t>Le pain est encore tiède. La croûte fait un petit bruit. Tu veux le pain ? Oui. S'il te plaît. Papa pose le pain dans les mains. Merci, papa. Bravo. Tu as demandé. Puis tu as dit merci. Le pain attend près du comptoir froid. On est encore à la fromagerie. Près de la boulangère. Tu as dit les mots ? Oui. Bonjour. S'il te plaît. Merci. Bravo, Raphaël. Tu as fait du bon travail. Raphaël range le pain, tout doux.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12395,10 +13250,34 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Corentin rejoint la boulangère à la fromagerie. Il a le pain. Bonjour, s'il te plaît, merci.</t>
-        </is>
-      </c>
-      <c r="AX66" t="inlineStr"/>
+          <t>narrateur|Le pain est encore tiède.
+narrateur|La croûte fait un petit bruit.
+papa|Tu veux le pain ?
+enfant-m|Oui.
+enfant-m|S'il te plaît.
+narrateur|Papa pose le pain dans les mains.
+enfant-m|Merci, papa.
+maman|Bravo.
+maman|Tu as demandé.
+maman|Puis tu as dit merci.
+narrateur|Le pain attend près du comptoir froid.
+narrateur|On est encore à la fromagerie.
+narrateur|Près de la boulangère.
+papa|Tu as dit les mots ?
+enfant-m|Oui.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+narrateur|Raphaël range le pain, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12423,7 +13302,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bravo, Raphaël. Tu as dit les trois mots. Raphaël a vécu à la fromagerie. Il a salué la boulangère. Il tient le pain. Le sachet reste tiède, contre le manteau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12563,7 +13442,16 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Raphaël.
+papa|Tu as dit les trois mots.
+narrateur|Raphaël a vécu à la fromagerie.
+narrateur|Il a salué la boulangère.
+narrateur|Il tient le pain.
+narrateur|Le sachet reste tiède, contre le manteau.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr"/>
@@ -12591,7 +13479,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Corentin rejoint la boulangère à la fromagerie. Il a une pomme. Bonjour, s'il te plaît, merci.</t>
+          <t>La pomme est rouge, toute lisse. Un point jaune brille sur la peau. Tu veux la pomme ? S'il te plaît. Maman la pose, tout doux. Merci, maman. Bravo, Raphaël. Tu as dit s'il te plaît. Et merci, maintenant. Merci. La pomme brille, sur le marbre froid. On est encore à la fromagerie. Près de la boulangère. Tu as dit les mots ? Oui. Bonjour. S'il te plaît. Merci. Bravo, Raphaël. Tu as fait du bon travail. Raphaël range la pomme, tout doux.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12731,7 +13619,27 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Corentin rejoint la boulangère à la fromagerie. Il a une pomme. Bonjour, s'il te plaît, merci.</t>
+          <t>narrateur|La pomme est rouge, toute lisse.
+narrateur|Un point jaune brille sur la peau.
+maman|Tu veux la pomme ?
+enfant-m|S'il te plaît.
+narrateur|Maman la pose, tout doux.
+enfant-m|Merci, maman.
+papa|Bravo, Raphaël.
+papa|Tu as dit s'il te plaît.
+maman|Et merci, maintenant.
+enfant-m|Merci.
+narrateur|La pomme brille, sur le marbre froid.
+narrateur|On est encore à la fromagerie.
+narrateur|Près de la boulangère.
+papa|Tu as dit les mots ?
+enfant-m|Oui.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+narrateur|Raphaël range la pomme, tout doux.</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr"/>
@@ -12759,7 +13667,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bravo, Raphaël. Tu as dit les trois mots. Raphaël a vécu à la fromagerie. Il a salué la boulangère. Il tient la pomme. La pomme garde un point jaune, tout petit. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12899,7 +13807,16 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Raphaël.
+papa|Tu as dit les trois mots.
+narrateur|Raphaël a vécu à la fromagerie.
+narrateur|Il a salué la boulangère.
+narrateur|Il tient la pomme.
+narrateur|La pomme garde un point jaune, tout petit.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr"/>
@@ -12927,7 +13844,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Corentin rejoint la boulangère à la fromagerie. Il a un fromage. Bonjour, s'il te plaît, merci.</t>
+          <t>Le fromage est dans un papier blanc. Le papier fait un bruit doux. On prend le fromage ? Oui. S'il te plaît. Papa tend le paquet, tout lentement. Merci. Bravo. Tu as dit les mots. On dit merci, encore une fois. Merci, papa. La boulangère touche le papier blanc. On est encore à la fromagerie. Près de la boulangère. Tu as dit les mots ? Oui. Bonjour. S'il te plaît. Merci. Bravo, Raphaël. Tu as fait du bon travail. Raphaël range le fromage, tout doux.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13067,10 +13984,35 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Corentin rejoint la boulangère à la fromagerie. Il a un fromage. Bonjour, s'il te plaît, merci.</t>
-        </is>
-      </c>
-      <c r="AX70" t="inlineStr"/>
+          <t>narrateur|Le fromage est dans un papier blanc.
+narrateur|Le papier fait un bruit doux.
+papa|On prend le fromage ?
+enfant-m|Oui.
+enfant-m|S'il te plaît.
+narrateur|Papa tend le paquet, tout lentement.
+enfant-m|Merci.
+maman|Bravo.
+maman|Tu as dit les mots.
+papa|On dit merci, encore une fois.
+enfant-m|Merci, papa.
+narrateur|La boulangère touche le papier blanc.
+narrateur|On est encore à la fromagerie.
+narrateur|Près de la boulangère.
+papa|Tu as dit les mots ?
+enfant-m|Oui.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+narrateur|Raphaël range le fromage, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>papier</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13095,7 +14037,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bravo, Raphaël. Tu as dit les trois mots. Raphaël a vécu à la fromagerie. Il a salué la boulangère. Il tient le fromage. Le papier blanc se tait, dans le panier. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13235,7 +14177,16 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Raphaël.
+papa|Tu as dit les trois mots.
+narrateur|Raphaël a vécu à la fromagerie.
+narrateur|Il a salué la boulangère.
+narrateur|Il tient le fromage.
+narrateur|Le papier blanc se tait, dans le panier.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr"/>
@@ -13263,7 +14214,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Corentin dit bonjour. S'il te plaît. Merci.</t>
+          <t>Le voisin tient un panier d'osier. Le panier sent le bois, un peu. On dit bonjour au voisin. Bonjour. Le voisin incline un peu la tête. Tu veux passer ? Oui. S'il te plaît. Raphaël recule, tout doux. Merci. Bravo. Tu as dit les mots. On dit s'il te plaît. On dit merci. Une anse du panier craque, tout petit. Le panier d'osier sent le lait. On est encore à la fromagerie. On dit s'il te plaît. On dit merci.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13403,7 +14354,25 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|Corentin dit bonjour. S'il te plaît. Merci.</t>
+          <t>narrateur|Le voisin tient un panier d'osier.
+narrateur|Le panier sent le bois, un peu.
+papa|On dit bonjour au voisin.
+enfant-m|Bonjour.
+narrateur|Le voisin incline un peu la tête.
+maman|Tu veux passer ?
+enfant-m|Oui.
+enfant-m|S'il te plaît.
+narrateur|Raphaël recule, tout doux.
+enfant-m|Merci.
+papa|Bravo.
+papa|Tu as dit les mots.
+maman|On dit s'il te plaît.
+maman|On dit merci.
+narrateur|Une anse du panier craque, tout petit.
+narrateur|Le panier d'osier sent le lait.
+narrateur|On est encore à la fromagerie.
+maman|On dit s'il te plaît.
+maman|On dit merci.</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr"/>
@@ -13431,7 +14400,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le pain, une pomme, ou un fromage.</t>
+          <t>Trois choses brillent, dans le panier. Le pain, une pomme, ou un fromage ? On dit encore les mots.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -13595,7 +14564,9 @@
       <c r="AV73" s="2" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le pain, une pomme, ou un fromage.</t>
+          <t>narrateur|Trois choses brillent, dans le panier.
+papa|Le pain, une pomme, ou un fromage ?
+maman|On dit encore les mots.</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr"/>
@@ -13623,7 +14594,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Corentin rejoint le voisin à la fromagerie. Il a le pain. Bonjour, s'il te plaît, merci.</t>
+          <t>Le pain est encore tiède. La croûte fait un petit bruit. Tu veux le pain ? Oui. S'il te plaît. Papa pose le pain dans les mains. Merci, papa. Bravo. Tu as demandé. Puis tu as dit merci. Le voisin pose le pain, tout près. On est encore à la fromagerie. Près de le voisin. Tu as dit les mots ? Oui. Bonjour. S'il te plaît. Merci. Bravo, Raphaël. Tu as fait du bon travail. Raphaël range le pain, tout doux.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13763,10 +14734,34 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Corentin rejoint le voisin à la fromagerie. Il a le pain. Bonjour, s'il te plaît, merci.</t>
-        </is>
-      </c>
-      <c r="AX74" t="inlineStr"/>
+          <t>narrateur|Le pain est encore tiède.
+narrateur|La croûte fait un petit bruit.
+papa|Tu veux le pain ?
+enfant-m|Oui.
+enfant-m|S'il te plaît.
+narrateur|Papa pose le pain dans les mains.
+enfant-m|Merci, papa.
+maman|Bravo.
+maman|Tu as demandé.
+maman|Puis tu as dit merci.
+narrateur|Le voisin pose le pain, tout près.
+narrateur|On est encore à la fromagerie.
+narrateur|Près de le voisin.
+papa|Tu as dit les mots ?
+enfant-m|Oui.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+narrateur|Raphaël range le pain, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13791,7 +14786,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bravo, Raphaël. Tu as dit les trois mots. Raphaël a vécu à la fromagerie. Il a salué le voisin. Il tient le pain. Le sachet reste tiède, contre le manteau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -13931,7 +14926,16 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Raphaël.
+papa|Tu as dit les trois mots.
+narrateur|Raphaël a vécu à la fromagerie.
+narrateur|Il a salué le voisin.
+narrateur|Il tient le pain.
+narrateur|Le sachet reste tiède, contre le manteau.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr"/>
@@ -13959,7 +14963,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Corentin rejoint le voisin à la fromagerie. Il a une pomme. Bonjour, s'il te plaît, merci.</t>
+          <t>La pomme est rouge, toute lisse. Un point jaune brille sur la peau. Tu veux la pomme ? S'il te plaît. Maman la pose, tout doux. Merci, maman. Bravo, Raphaël. Tu as dit s'il te plaît. Et merci, maintenant. Merci. La pomme fait un bruit, sur le marbre. On est encore à la fromagerie. Près de le voisin. Tu as dit les mots ? Oui. Bonjour. S'il te plaît. Merci. Bravo, Raphaël. Tu as fait du bon travail. Raphaël range la pomme, tout doux.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14099,7 +15103,27 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Corentin rejoint le voisin à la fromagerie. Il a une pomme. Bonjour, s'il te plaît, merci.</t>
+          <t>narrateur|La pomme est rouge, toute lisse.
+narrateur|Un point jaune brille sur la peau.
+maman|Tu veux la pomme ?
+enfant-m|S'il te plaît.
+narrateur|Maman la pose, tout doux.
+enfant-m|Merci, maman.
+papa|Bravo, Raphaël.
+papa|Tu as dit s'il te plaît.
+maman|Et merci, maintenant.
+enfant-m|Merci.
+narrateur|La pomme fait un bruit, sur le marbre.
+narrateur|On est encore à la fromagerie.
+narrateur|Près de le voisin.
+papa|Tu as dit les mots ?
+enfant-m|Oui.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+narrateur|Raphaël range la pomme, tout doux.</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr"/>
@@ -14127,7 +15151,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bravo, Raphaël. Tu as dit les trois mots. Raphaël a vécu à la fromagerie. Il a salué le voisin. Il tient la pomme. La pomme garde un point jaune, tout petit. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14267,7 +15291,16 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Raphaël.
+papa|Tu as dit les trois mots.
+narrateur|Raphaël a vécu à la fromagerie.
+narrateur|Il a salué le voisin.
+narrateur|Il tient la pomme.
+narrateur|La pomme garde un point jaune, tout petit.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr"/>
@@ -14295,7 +15328,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Corentin rejoint le voisin à la fromagerie. Il a un fromage. Bonjour, s'il te plaît, merci.</t>
+          <t>Le fromage est dans un papier blanc. Le papier fait un bruit doux. On prend le fromage ? Oui. S'il te plaît. Papa tend le paquet, tout lentement. Merci. Bravo. Tu as dit les mots. On dit merci, encore une fois. Merci, papa. Le voisin sent le fromage, tout doux. On est encore à la fromagerie. Près de le voisin. Tu as dit les mots ? Oui. Bonjour. S'il te plaît. Merci. Bravo, Raphaël. Tu as fait du bon travail. Raphaël range le fromage, tout doux.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14435,10 +15468,35 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|Corentin rejoint le voisin à la fromagerie. Il a un fromage. Bonjour, s'il te plaît, merci.</t>
-        </is>
-      </c>
-      <c r="AX78" t="inlineStr"/>
+          <t>narrateur|Le fromage est dans un papier blanc.
+narrateur|Le papier fait un bruit doux.
+papa|On prend le fromage ?
+enfant-m|Oui.
+enfant-m|S'il te plaît.
+narrateur|Papa tend le paquet, tout lentement.
+enfant-m|Merci.
+maman|Bravo.
+maman|Tu as dit les mots.
+papa|On dit merci, encore une fois.
+enfant-m|Merci, papa.
+narrateur|Le voisin sent le fromage, tout doux.
+narrateur|On est encore à la fromagerie.
+narrateur|Près de le voisin.
+papa|Tu as dit les mots ?
+enfant-m|Oui.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+narrateur|Raphaël range le fromage, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>papier</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14463,7 +15521,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bravo, Raphaël. Tu as dit les trois mots. Raphaël a vécu à la fromagerie. Il a salué le voisin. Il tient le fromage. Le papier blanc se tait, dans le panier. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14603,7 +15661,16 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Raphaël.
+papa|Tu as dit les trois mots.
+narrateur|Raphaël a vécu à la fromagerie.
+narrateur|Il a salué le voisin.
+narrateur|Il tient le fromage.
+narrateur|Le papier blanc se tait, dans le panier.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr"/>
@@ -14631,7 +15698,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Corentin dit bonjour. S'il te plaît. Merci.</t>
+          <t>La maîtresse a un sac, tout simple. Bonjour, Raphaël. Bonjour. On dit s'il te plaît. Tu veux saluer encore ? Oui. S'il te plaît. Merci, Raphaël. Merci. Bravo. Tu as dit bonjour. On dit les trois mots. Le sac de la maîtresse sent le pain. Le sac pose sur le marbre froid. On est encore à la fromagerie. On dit s'il te plaît. On dit merci.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14771,7 +15838,23 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|Corentin dit bonjour. S'il te plaît. Merci.</t>
+          <t>narrateur|La maîtresse a un sac, tout simple.
+maitresse|Bonjour, Raphaël.
+enfant-m|Bonjour.
+maman|On dit s'il te plaît.
+papa|Tu veux saluer encore ?
+enfant-m|Oui.
+enfant-m|S'il te plaît.
+maitresse|Merci, Raphaël.
+enfant-m|Merci.
+papa|Bravo.
+papa|Tu as dit bonjour.
+maman|On dit les trois mots.
+narrateur|Le sac de la maîtresse sent le pain.
+narrateur|Le sac pose sur le marbre froid.
+narrateur|On est encore à la fromagerie.
+maman|On dit s'il te plaît.
+maman|On dit merci.</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr"/>
@@ -14799,7 +15882,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le pain, une pomme, ou un fromage.</t>
+          <t>Trois choses brillent, dans le panier. Le pain, une pomme, ou un fromage ? On dit encore les mots.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -14963,7 +16046,9 @@
       <c r="AV81" s="2" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le pain, une pomme, ou un fromage.</t>
+          <t>narrateur|Trois choses brillent, dans le panier.
+papa|Le pain, une pomme, ou un fromage ?
+maman|On dit encore les mots.</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr"/>
@@ -14991,7 +16076,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Corentin rejoint la maîtresse à la fromagerie. Il a le pain. Bonjour, s'il te plaît, merci.</t>
+          <t>Le pain est encore tiède. La croûte fait un petit bruit. Tu veux le pain ? Oui. S'il te plaît. Papa pose le pain dans les mains. Merci, papa. Bravo. Tu as demandé. Puis tu as dit merci. La maîtresse range le pain, tout près. On est encore à la fromagerie. Près de la maîtresse. Tu as dit les mots ? Oui. Bonjour. S'il te plaît. Merci. Bravo, Raphaël. Tu as fait du bon travail. Raphaël range le pain, tout doux.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15131,10 +16216,34 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|Corentin rejoint la maîtresse à la fromagerie. Il a le pain. Bonjour, s'il te plaît, merci.</t>
-        </is>
-      </c>
-      <c r="AX82" t="inlineStr"/>
+          <t>narrateur|Le pain est encore tiède.
+narrateur|La croûte fait un petit bruit.
+papa|Tu veux le pain ?
+enfant-m|Oui.
+enfant-m|S'il te plaît.
+narrateur|Papa pose le pain dans les mains.
+enfant-m|Merci, papa.
+maman|Bravo.
+maman|Tu as demandé.
+maman|Puis tu as dit merci.
+narrateur|La maîtresse range le pain, tout près.
+narrateur|On est encore à la fromagerie.
+narrateur|Près de la maîtresse.
+papa|Tu as dit les mots ?
+enfant-m|Oui.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+narrateur|Raphaël range le pain, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15159,7 +16268,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bravo, Raphaël. Tu as dit les trois mots. Raphaël a vécu à la fromagerie. Il a salué la maîtresse. Il tient le pain. Le sachet reste tiède, contre le manteau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15299,7 +16408,16 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Raphaël.
+papa|Tu as dit les trois mots.
+narrateur|Raphaël a vécu à la fromagerie.
+narrateur|Il a salué la maîtresse.
+narrateur|Il tient le pain.
+narrateur|Le sachet reste tiède, contre le manteau.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr"/>
@@ -15327,7 +16445,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Corentin rejoint la maîtresse à la fromagerie. Il a une pomme. Bonjour, s'il te plaît, merci.</t>
+          <t>La pomme est rouge, toute lisse. Un point jaune brille sur la peau. Tu veux la pomme ? S'il te plaît. Maman la pose, tout doux. Merci, maman. Bravo, Raphaël. Tu as dit s'il te plaît. Et merci, maintenant. Merci. La pomme attend dans le sac. On est encore à la fromagerie. Près de la maîtresse. Tu as dit les mots ? Oui. Bonjour. S'il te plaît. Merci. Bravo, Raphaël. Tu as fait du bon travail. Raphaël range la pomme, tout doux.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15467,7 +16585,27 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|Corentin rejoint la maîtresse à la fromagerie. Il a une pomme. Bonjour, s'il te plaît, merci.</t>
+          <t>narrateur|La pomme est rouge, toute lisse.
+narrateur|Un point jaune brille sur la peau.
+maman|Tu veux la pomme ?
+enfant-m|S'il te plaît.
+narrateur|Maman la pose, tout doux.
+enfant-m|Merci, maman.
+papa|Bravo, Raphaël.
+papa|Tu as dit s'il te plaît.
+maman|Et merci, maintenant.
+enfant-m|Merci.
+narrateur|La pomme attend dans le sac.
+narrateur|On est encore à la fromagerie.
+narrateur|Près de la maîtresse.
+papa|Tu as dit les mots ?
+enfant-m|Oui.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+narrateur|Raphaël range la pomme, tout doux.</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr"/>
@@ -15495,7 +16633,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bravo, Raphaël. Tu as dit les trois mots. Raphaël a vécu à la fromagerie. Il a salué la maîtresse. Il tient la pomme. La pomme garde un point jaune, tout petit. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15635,7 +16773,16 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Raphaël.
+papa|Tu as dit les trois mots.
+narrateur|Raphaël a vécu à la fromagerie.
+narrateur|Il a salué la maîtresse.
+narrateur|Il tient la pomme.
+narrateur|La pomme garde un point jaune, tout petit.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr"/>
@@ -15663,7 +16810,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Corentin rejoint la maîtresse à la fromagerie. Il a un fromage. Bonjour, s'il te plaît, merci.</t>
+          <t>Le fromage est dans un papier blanc. Le papier fait un bruit doux. On prend le fromage ? Oui. S'il te plaît. Papa tend le paquet, tout lentement. Merci. Bravo. Tu as dit les mots. On dit merci, encore une fois. Merci, papa. Le papier du fromage fait un bruit doux. On est encore à la fromagerie. Près de la maîtresse. Tu as dit les mots ? Oui. Bonjour. S'il te plaît. Merci. Bravo, Raphaël. Tu as fait du bon travail. Raphaël range le fromage, tout doux.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15803,10 +16950,35 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|Corentin rejoint la maîtresse à la fromagerie. Il a un fromage. Bonjour, s'il te plaît, merci.</t>
-        </is>
-      </c>
-      <c r="AX86" t="inlineStr"/>
+          <t>narrateur|Le fromage est dans un papier blanc.
+narrateur|Le papier fait un bruit doux.
+papa|On prend le fromage ?
+enfant-m|Oui.
+enfant-m|S'il te plaît.
+narrateur|Papa tend le paquet, tout lentement.
+enfant-m|Merci.
+maman|Bravo.
+maman|Tu as dit les mots.
+papa|On dit merci, encore une fois.
+enfant-m|Merci, papa.
+narrateur|Le papier du fromage fait un bruit doux.
+narrateur|On est encore à la fromagerie.
+narrateur|Près de la maîtresse.
+papa|Tu as dit les mots ?
+enfant-m|Oui.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+narrateur|Raphaël range le fromage, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>papier</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15831,7 +17003,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bravo, Raphaël. Tu as dit les trois mots. Raphaël a vécu à la fromagerie. Il a salué la maîtresse. Il tient le fromage. Le papier blanc se tait, dans le panier. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -15971,7 +17143,16 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Raphaël.
+papa|Tu as dit les trois mots.
+narrateur|Raphaël a vécu à la fromagerie.
+narrateur|Il a salué la maîtresse.
+narrateur|Il tient le fromage.
+narrateur|Le papier blanc se tait, dans le panier.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr"/>
@@ -15993,7 +17174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16031,6 +17212,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>
